--- a/bulk_up/plantilla_products.xlsx
+++ b/bulk_up/plantilla_products.xlsx
@@ -1,26 +1,42 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Robert\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Proyectos\Apudig\Proyecto\apudig_mvp\bulk_up\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55BC2AD2-C0B1-47A1-8B59-05DAA43C7030}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA3405AC-EA14-42F4-927B-537070946EFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="780" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2355" yWindow="2355" windowWidth="20115" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="plantilla" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="822" uniqueCount="393">
   <si>
     <t>sku</t>
   </si>
@@ -125,16 +141,1096 @@
   </si>
   <si>
     <t>Caudal: 800-3270 L/H Alcance: 12-19M Presión: 1.75 - 5.0 Bar</t>
+  </si>
+  <si>
+    <t>RA02001</t>
+  </si>
+  <si>
+    <t>RA02002</t>
+  </si>
+  <si>
+    <t>RA02003</t>
+  </si>
+  <si>
+    <t>RA02004</t>
+  </si>
+  <si>
+    <t>RA02005</t>
+  </si>
+  <si>
+    <t>RA02006</t>
+  </si>
+  <si>
+    <t>RA02007</t>
+  </si>
+  <si>
+    <t>RA02008</t>
+  </si>
+  <si>
+    <t>RA02009</t>
+  </si>
+  <si>
+    <t>RA02010</t>
+  </si>
+  <si>
+    <t>RA02011</t>
+  </si>
+  <si>
+    <t>RA02012</t>
+  </si>
+  <si>
+    <t>RA02013</t>
+  </si>
+  <si>
+    <t>RA02014</t>
+  </si>
+  <si>
+    <t>RA02015</t>
+  </si>
+  <si>
+    <t>RA02016</t>
+  </si>
+  <si>
+    <t>RA02017</t>
+  </si>
+  <si>
+    <t>RA02018</t>
+  </si>
+  <si>
+    <t>RA02019</t>
+  </si>
+  <si>
+    <t>RA02020</t>
+  </si>
+  <si>
+    <t>RA02021</t>
+  </si>
+  <si>
+    <t>RA02022</t>
+  </si>
+  <si>
+    <t>RA02023</t>
+  </si>
+  <si>
+    <t>RA02024</t>
+  </si>
+  <si>
+    <t>RA02025</t>
+  </si>
+  <si>
+    <t>RA02026</t>
+  </si>
+  <si>
+    <t>RA02027</t>
+  </si>
+  <si>
+    <t>RA02028</t>
+  </si>
+  <si>
+    <t>RA02029</t>
+  </si>
+  <si>
+    <t>RA02030</t>
+  </si>
+  <si>
+    <t>RA02031</t>
+  </si>
+  <si>
+    <t>RA02032</t>
+  </si>
+  <si>
+    <t>RA02033</t>
+  </si>
+  <si>
+    <t>RA02034</t>
+  </si>
+  <si>
+    <t>RA02035</t>
+  </si>
+  <si>
+    <t>RA02036</t>
+  </si>
+  <si>
+    <t>RA02037</t>
+  </si>
+  <si>
+    <t>RA02038</t>
+  </si>
+  <si>
+    <t>RA02039</t>
+  </si>
+  <si>
+    <t>RA02040</t>
+  </si>
+  <si>
+    <t>RA02041</t>
+  </si>
+  <si>
+    <t>RA02042</t>
+  </si>
+  <si>
+    <t>RA02043</t>
+  </si>
+  <si>
+    <t>RA02044</t>
+  </si>
+  <si>
+    <t>RA02045</t>
+  </si>
+  <si>
+    <t>RA02046</t>
+  </si>
+  <si>
+    <t>RA02047</t>
+  </si>
+  <si>
+    <t>RA02048</t>
+  </si>
+  <si>
+    <t>RA02049</t>
+  </si>
+  <si>
+    <t>RA02050</t>
+  </si>
+  <si>
+    <t>RA02051</t>
+  </si>
+  <si>
+    <t>RA02052</t>
+  </si>
+  <si>
+    <t>RA02053</t>
+  </si>
+  <si>
+    <t>RA02054</t>
+  </si>
+  <si>
+    <t>RA02055</t>
+  </si>
+  <si>
+    <t>RA02056</t>
+  </si>
+  <si>
+    <t>RA02057</t>
+  </si>
+  <si>
+    <t>RA02058</t>
+  </si>
+  <si>
+    <t>RA02059</t>
+  </si>
+  <si>
+    <t>RA02060</t>
+  </si>
+  <si>
+    <t>RA02061</t>
+  </si>
+  <si>
+    <t>RA02062</t>
+  </si>
+  <si>
+    <t>RA02063</t>
+  </si>
+  <si>
+    <t>RA02064</t>
+  </si>
+  <si>
+    <t>RA02065</t>
+  </si>
+  <si>
+    <t>RA02066</t>
+  </si>
+  <si>
+    <t>RA02067</t>
+  </si>
+  <si>
+    <t>RA02068</t>
+  </si>
+  <si>
+    <t>RA02069</t>
+  </si>
+  <si>
+    <t>RA02070</t>
+  </si>
+  <si>
+    <t>RA02071</t>
+  </si>
+  <si>
+    <t>RA02072</t>
+  </si>
+  <si>
+    <t>RA02073</t>
+  </si>
+  <si>
+    <t>RA02074</t>
+  </si>
+  <si>
+    <t>RA02075</t>
+  </si>
+  <si>
+    <t>RA02076</t>
+  </si>
+  <si>
+    <t>RA02077</t>
+  </si>
+  <si>
+    <t>RA02078</t>
+  </si>
+  <si>
+    <t>RA02079</t>
+  </si>
+  <si>
+    <t>RA02080</t>
+  </si>
+  <si>
+    <t>RA02081</t>
+  </si>
+  <si>
+    <t>RA02082</t>
+  </si>
+  <si>
+    <t>RA02083</t>
+  </si>
+  <si>
+    <t>RA02084</t>
+  </si>
+  <si>
+    <t>RA02085</t>
+  </si>
+  <si>
+    <t>RA02086</t>
+  </si>
+  <si>
+    <t>RA02087</t>
+  </si>
+  <si>
+    <t>RA02088</t>
+  </si>
+  <si>
+    <t>RA02089</t>
+  </si>
+  <si>
+    <t>RA02090</t>
+  </si>
+  <si>
+    <t>RA02091</t>
+  </si>
+  <si>
+    <t>RA02092</t>
+  </si>
+  <si>
+    <t>RA02093</t>
+  </si>
+  <si>
+    <t>RA02094</t>
+  </si>
+  <si>
+    <t>RA02095</t>
+  </si>
+  <si>
+    <t>RA02096</t>
+  </si>
+  <si>
+    <t>RA02097</t>
+  </si>
+  <si>
+    <t>RA02098</t>
+  </si>
+  <si>
+    <t>RA02099</t>
+  </si>
+  <si>
+    <t>RA02100</t>
+  </si>
+  <si>
+    <t>RA02101</t>
+  </si>
+  <si>
+    <t>RA02102</t>
+  </si>
+  <si>
+    <t>RA02103</t>
+  </si>
+  <si>
+    <t>RA02104</t>
+  </si>
+  <si>
+    <t>RA02105</t>
+  </si>
+  <si>
+    <t>RA02106</t>
+  </si>
+  <si>
+    <t>RA02107</t>
+  </si>
+  <si>
+    <t>RA02108</t>
+  </si>
+  <si>
+    <t>RA02109</t>
+  </si>
+  <si>
+    <t>RA02110</t>
+  </si>
+  <si>
+    <t>RA02111</t>
+  </si>
+  <si>
+    <t>RA02112</t>
+  </si>
+  <si>
+    <t>RA02113</t>
+  </si>
+  <si>
+    <t>RA03001</t>
+  </si>
+  <si>
+    <t>RA03002</t>
+  </si>
+  <si>
+    <t>RA03003</t>
+  </si>
+  <si>
+    <t>RA03004</t>
+  </si>
+  <si>
+    <t>RA03005</t>
+  </si>
+  <si>
+    <t>RA03006</t>
+  </si>
+  <si>
+    <t>RA03007</t>
+  </si>
+  <si>
+    <t>RA03008</t>
+  </si>
+  <si>
+    <t>RA03009</t>
+  </si>
+  <si>
+    <t>RA03010</t>
+  </si>
+  <si>
+    <t>RA03011</t>
+  </si>
+  <si>
+    <t>RA03012</t>
+  </si>
+  <si>
+    <t>RA03013</t>
+  </si>
+  <si>
+    <t>RA03014</t>
+  </si>
+  <si>
+    <t>RA03015</t>
+  </si>
+  <si>
+    <t>RA03016</t>
+  </si>
+  <si>
+    <t>RA03017</t>
+  </si>
+  <si>
+    <t>RA03018</t>
+  </si>
+  <si>
+    <t>RA03019</t>
+  </si>
+  <si>
+    <t>RA03020</t>
+  </si>
+  <si>
+    <t>RA03021</t>
+  </si>
+  <si>
+    <t>RA03022</t>
+  </si>
+  <si>
+    <t>RA03023</t>
+  </si>
+  <si>
+    <t>RA03024</t>
+  </si>
+  <si>
+    <t>RA03025</t>
+  </si>
+  <si>
+    <t>RA03026</t>
+  </si>
+  <si>
+    <t>RA03027</t>
+  </si>
+  <si>
+    <t>RA03028</t>
+  </si>
+  <si>
+    <t>RA03029</t>
+  </si>
+  <si>
+    <t>RA03030</t>
+  </si>
+  <si>
+    <t>RA03031</t>
+  </si>
+  <si>
+    <t>RA03032</t>
+  </si>
+  <si>
+    <t>RA03033</t>
+  </si>
+  <si>
+    <t>RA03034</t>
+  </si>
+  <si>
+    <t>RA03035</t>
+  </si>
+  <si>
+    <t>RA03036</t>
+  </si>
+  <si>
+    <t>RA03037</t>
+  </si>
+  <si>
+    <t>RA03038</t>
+  </si>
+  <si>
+    <t>RA03039</t>
+  </si>
+  <si>
+    <t>RA03040</t>
+  </si>
+  <si>
+    <t>RA03041</t>
+  </si>
+  <si>
+    <t>RA03042</t>
+  </si>
+  <si>
+    <t>RA03043</t>
+  </si>
+  <si>
+    <t>RA03044</t>
+  </si>
+  <si>
+    <t>RA03045</t>
+  </si>
+  <si>
+    <t>RA03046</t>
+  </si>
+  <si>
+    <t>RA03047</t>
+  </si>
+  <si>
+    <t>RA03048</t>
+  </si>
+  <si>
+    <t>RA03049</t>
+  </si>
+  <si>
+    <t>RA03050</t>
+  </si>
+  <si>
+    <t>RA03051</t>
+  </si>
+  <si>
+    <t>RA03052</t>
+  </si>
+  <si>
+    <t>RA03053</t>
+  </si>
+  <si>
+    <t>RA03054</t>
+  </si>
+  <si>
+    <t>RA03055</t>
+  </si>
+  <si>
+    <t>RA03056</t>
+  </si>
+  <si>
+    <t>RA03057</t>
+  </si>
+  <si>
+    <t>RA03058</t>
+  </si>
+  <si>
+    <t>RA03059</t>
+  </si>
+  <si>
+    <t>RA03060</t>
+  </si>
+  <si>
+    <t>RA03061</t>
+  </si>
+  <si>
+    <t>RA03062</t>
+  </si>
+  <si>
+    <t>RA03063</t>
+  </si>
+  <si>
+    <t>RA03064</t>
+  </si>
+  <si>
+    <t>Adaptador Enlace R/Hembra 110 x 4" PN16 HDPE POELSAN</t>
+  </si>
+  <si>
+    <t>Adaptador Enlace R/Hembra 20 x 1/2" PN16 HDPE POELSAN</t>
+  </si>
+  <si>
+    <t>Adaptador Enlace R/Hembra 25 x 3/4" PN16 HDPE POELSAN</t>
+  </si>
+  <si>
+    <t>Adaptador Enlace R/Hembra 32 x 1" PN16 HDPE POELSAN</t>
+  </si>
+  <si>
+    <t>Adaptador Enlace R/Hembra 50 x 1 1/2" PN16 HDPE POELSAN</t>
+  </si>
+  <si>
+    <t>Adaptador Enlace R/Hembra 63 x 2" PN16 HDPE POELSAN</t>
+  </si>
+  <si>
+    <t>Adaptador Enlace R/Hembra 90 x 3" PN16 HDPE POELSAN</t>
+  </si>
+  <si>
+    <t>Adaptador Enlace R/Macho 110 x 4" PN16 HDPE POELSAN</t>
+  </si>
+  <si>
+    <t>Adaptador Enlace R/Macho 20 x 1/2" PN16 HDPE POELSAN</t>
+  </si>
+  <si>
+    <t>Adaptador Enlace R/Macho 25 x 3/4" PN16 HDPE POELSAN</t>
+  </si>
+  <si>
+    <t>Adaptador Enlace R/Macho 32 x 1" PN16 HDPE POELSAN</t>
+  </si>
+  <si>
+    <t>Adaptador Enlace R/Macho 50 x 1 1/2" PN16 HDPE POELSAN</t>
+  </si>
+  <si>
+    <t>Adaptador Enlace R/Macho 63 x 2" PN16 HDPE POELSAN</t>
+  </si>
+  <si>
+    <t>Adaptador Enlace R/Macho 75 x 2 1/2" PN16 HDPE SENKRON</t>
+  </si>
+  <si>
+    <t>Adaptador Enlace R/Macho 90 x 3" PN16 HDPE POELSAN</t>
+  </si>
+  <si>
+    <t>Enlace Codo 110 x 110 mm Bocas Iguales 90° HDPE GPA</t>
+  </si>
+  <si>
+    <t>Enlace Codo 110 x 110 mm Bocas Iguales 90° PN16 HDPE POELSAN</t>
+  </si>
+  <si>
+    <t>Enlace Codo 20 x 20 mm Bocas Iguales 90° PN16 HDPE POELSAN</t>
+  </si>
+  <si>
+    <t>Enlace Codo 25 x 25 mm Bocas Iguales 90°  PN16 HDPE POELSAN</t>
+  </si>
+  <si>
+    <t>Enlace Codo 32 x 32 mm Bocas Iguales 90° PN16 HDPE FITSA</t>
+  </si>
+  <si>
+    <t>Enlace Codo 32 x 32 mm Bocas Iguales 90° PN16 HDPE POELSAN</t>
+  </si>
+  <si>
+    <t>Enlace Codo 50 x 50 mm Bocas Iguales 90° PN16 HDPE POELSAN</t>
+  </si>
+  <si>
+    <t>Enlace Codo 63 x 63 mm Bocas Iguales 90° HDPE KIWA</t>
+  </si>
+  <si>
+    <t>Enlace Codo 63 x 63 mm Bocas Iguales 90° PN16 HDPE POELSAN</t>
+  </si>
+  <si>
+    <t>Enlace Codo 90 x 90 mm Bocas Iguales 90° PN16 HDPE POELSAN</t>
+  </si>
+  <si>
+    <t>Enlace Codo R/Hembra 110 x 4" PN16 90° HDPE POELSAN</t>
+  </si>
+  <si>
+    <t>Enlace Codo R/Hembra 20 x 1/2" PN16 90° HDPE POELSAN</t>
+  </si>
+  <si>
+    <t>Enlace Codo R/Hembra 25 x 3/4" PN16 90° HDPE POELSAN</t>
+  </si>
+  <si>
+    <t>Enlace Codo R/Hembra 32 x 1" PN16 90° HDPE POELSAN</t>
+  </si>
+  <si>
+    <t>Enlace Codo R/Hembra 32 x 3/4" PN16 90° HDPE POELSAN</t>
+  </si>
+  <si>
+    <t>Enlace Codo R/Hembra 50 x 1 1/2" PN16 90° HDPE FITSA</t>
+  </si>
+  <si>
+    <t>Enlace Codo R/Hembra 50 x 1 1/2" PN16 90° HDPE POELSAN</t>
+  </si>
+  <si>
+    <t>Enlace Codo R/Hembra 63 x 2" PN16 90° HDPE POELSAN</t>
+  </si>
+  <si>
+    <t>Enlace Codo R/Hembra 90 x 3" PN16 90° HDPE POELSAN</t>
+  </si>
+  <si>
+    <t>Enlace Tapon 110 mm PN16 HDPE POELSAN</t>
+  </si>
+  <si>
+    <t>Enlace Tapon 20 mm PN16 HDPE POELSAN</t>
+  </si>
+  <si>
+    <t>Enlace Tapon 25 mm PN16 HDPE POELSAN</t>
+  </si>
+  <si>
+    <t>Enlace Tapon 32 mm PN16 HDPE POELSAN</t>
+  </si>
+  <si>
+    <t>Enlace Tapon 50 mm PN16 HDPE POELSAN</t>
+  </si>
+  <si>
+    <t>Enlace Tapon 63 mm PN16 HDPE POELSAN</t>
+  </si>
+  <si>
+    <t>Enlace Tapon 90 mm PN16 HDPE POELSAN</t>
+  </si>
+  <si>
+    <t>Oring 25 mm HDPE</t>
+  </si>
+  <si>
+    <t>Oring 32 mm HDPE</t>
+  </si>
+  <si>
+    <t>Oring 50 mm HDPE</t>
+  </si>
+  <si>
+    <t>Oring 63 mm HDPE</t>
+  </si>
+  <si>
+    <t>Tee Bocas Iguales 110 x 110 x 110 mm PN16 HDPE POELSAN</t>
+  </si>
+  <si>
+    <t>Tee Bocas Iguales 110 x110 x 110 mm PN16 GPA</t>
+  </si>
+  <si>
+    <t>Tee Bocas Iguales 20 x 20 x 20 mm PN16 HDPE POELSAN</t>
+  </si>
+  <si>
+    <t>Tee Bocas Iguales 25 x 25 x 25 mm PN16 HDPE POELSAN</t>
+  </si>
+  <si>
+    <t>Tee Bocas Iguales 32 x 32 x 32 mm PN16 HDPE POELSAN</t>
+  </si>
+  <si>
+    <t>Tee Bocas Iguales 50 x 50 x 50 mm HDPE KIWA</t>
+  </si>
+  <si>
+    <t>Tee Bocas Iguales 50 x 50 x 50 mm PN16 HDPE FITSA</t>
+  </si>
+  <si>
+    <t>Tee Bocas Iguales 50 x 50 x 50 mm PN16 HDPE POELSAN</t>
+  </si>
+  <si>
+    <t>Tee Bocas Iguales 63 x 63 x 63 mm HDPE KIWA</t>
+  </si>
+  <si>
+    <t>Tee Bocas Iguales 63 x 63 x 63 mm PN16 HDPE POELSAN</t>
+  </si>
+  <si>
+    <t>Tee Bocas Iguales 90 x 90 x 90 mm PN16 HDPE POELSAN</t>
+  </si>
+  <si>
+    <t>Tee R/Hembra 110 x 4" x 110 mm PN16 HDPE POELSAN</t>
+  </si>
+  <si>
+    <t>Tee R/Hembra 20 x 1/2" x 20 mm  PN16 HDPE POELSAN</t>
+  </si>
+  <si>
+    <t>Tee R/Hembra 25 x 3/4" x 25 mm  PN16 HDPE POELSAN</t>
+  </si>
+  <si>
+    <t>Tee R/Hembra 25 x 3/4" x 25 mm PN16 HDPE FITSA</t>
+  </si>
+  <si>
+    <t>Tee R/Hembra 32 x 1" x 32 mm PN16 HDPE FITSA</t>
+  </si>
+  <si>
+    <t>Tee R/Hembra 32 x 1" x 32 mm PN16 HDPE POELSAN</t>
+  </si>
+  <si>
+    <t>Tee R/Hembra 32 x 3/4" x 32 mm  PN16 HDPE POELSAN</t>
+  </si>
+  <si>
+    <t>Tee R/Hembra 50 x 1 1/2" x 50 mm PN16 GPA</t>
+  </si>
+  <si>
+    <t>Tee R/Hembra 50 x 1 1/2" x 50 mm PN16 HDPE POELSAN</t>
+  </si>
+  <si>
+    <t>Tee R/Hembra 63 x 2" x 63 mm PN16 HDPE POELSAN</t>
+  </si>
+  <si>
+    <t>Tee R/Hembra 90 x 3" x 90 mm PN16 HDPE POELSAN</t>
+  </si>
+  <si>
+    <t>Tee Reducido 110 x 63 x 110 mm Bocas Iguales PN16 HDPE POELSAN</t>
+  </si>
+  <si>
+    <t>Tee Reducido 110 x 90 x 110 mm Bocas Iguales PN16 HDPE POELSAN</t>
+  </si>
+  <si>
+    <t>Tee Reducido 32 x 25 x 32 mm Bocas Iguales PN16 HDPE FITSA</t>
+  </si>
+  <si>
+    <t>Tee Reducido 32 x 25 x 32 mm Bocas Iguales PN16 HDPE POELSAN</t>
+  </si>
+  <si>
+    <t>Tee Reducido 50 x 32 x 50 mm Bocas Iguales PN16 HDPE POELSAN</t>
+  </si>
+  <si>
+    <t>Tee Reducido 63 x 32 x 63 mm Bocas Iguales PN16 HDPE FITSA</t>
+  </si>
+  <si>
+    <t>Tee Reducido 63 x 32 x 63 mm Bocas Iguales PN16 HDPE POELSAN</t>
+  </si>
+  <si>
+    <t>Tee Reducido 63 x 50 x 63 mm Bocas Iguales PN16 HDPE FITSA</t>
+  </si>
+  <si>
+    <t>Tee Reducido 63 x 50 x 63 mm Bocas Iguales PN16 HDPE POELSAN</t>
+  </si>
+  <si>
+    <t>Tee Reducido 90 x 63 x 90 mm Bocas Iguales PN16 HDPE POELSAN</t>
+  </si>
+  <si>
+    <t>Union Enlace Recto 110 x 110 mm PN16 GPA</t>
+  </si>
+  <si>
+    <t>Union Enlace Recto 110 x 110 mm PN16 HDPE POELSAN</t>
+  </si>
+  <si>
+    <t>Union Enlace Recto 20 x 20 mm PN16 HDPE POELSAN</t>
+  </si>
+  <si>
+    <t>Union Enlace Recto 25 x 25 mm PN16 HDPE POELSAN</t>
+  </si>
+  <si>
+    <t>Union Enlace Recto 32 x 32 mm PN16 HDPE POELSAN</t>
+  </si>
+  <si>
+    <t>Union Enlace Recto 50 x 50 mm PN16 HDPE POELSAN</t>
+  </si>
+  <si>
+    <t>Union Enlace Recto 50 x 50 mm PN6 VERD HDPE POELSAN</t>
+  </si>
+  <si>
+    <t>Union Enlace Recto 63 x 63 mm PN16 HDPE POELSAN</t>
+  </si>
+  <si>
+    <t>Union Enlace Recto 75 x  75 mm PN6 HDPE SENKRON</t>
+  </si>
+  <si>
+    <t>Union Enlace Recto 90 x 90 mm PN16 HDPE POELSAN</t>
+  </si>
+  <si>
+    <t>Union Enlace Reducido 110 x 63 mm PN16 HDPE POELSAN</t>
+  </si>
+  <si>
+    <t>Union Enlace Reducido 110 x 90 mm PN16 HDPE POELSAN</t>
+  </si>
+  <si>
+    <t>Union Enlace Reducido 25 x 20 mm PN16 HDPE POELSAN</t>
+  </si>
+  <si>
+    <t>Union Enlace Reducido 32 x 25 mm PN16 HDPE POELSAN</t>
+  </si>
+  <si>
+    <t>Union Enlace Reducido 50 x 32 mm PN16 HDPE POELSAN</t>
+  </si>
+  <si>
+    <t>Union Enlace Reducido 63 x 32 mm PN16 HDPE POELSAN</t>
+  </si>
+  <si>
+    <t>Union Enlace Reducido 63 x 50 mm PN16 HDPE POELSAN</t>
+  </si>
+  <si>
+    <t>Union Enlace Reducido 75 x 63 mm PN16 HDPE SENKRON</t>
+  </si>
+  <si>
+    <t>Union Enlace Reducido 90 x 63 mm PN16 HDPE POELSAN</t>
+  </si>
+  <si>
+    <t>Union Enlace Reducido 90 x 75 mm PN16 HDPE SENKRON</t>
+  </si>
+  <si>
+    <t>Union Enlace Recto 75 x  75 mm PN16 HDPE GPA</t>
+  </si>
+  <si>
+    <t>Union Enlace Reducido 75 x 63 mm PN16 HDPE GPA</t>
+  </si>
+  <si>
+    <t>Adaptador Enlace R/Hembra 50 x 1 1/2" PN16 HDPE</t>
+  </si>
+  <si>
+    <t>Adaptador Enlace R/Macho 25 x 3/4" PN16 HDPE</t>
+  </si>
+  <si>
+    <t>Adaptador Enlace R/Macho 90 x 3" R/Fina PN16 POELSAN</t>
+  </si>
+  <si>
+    <t>Adaptador Enlace R/Macho 110 x 4" R/Fina PN16 POELSAN</t>
+  </si>
+  <si>
+    <t>Union Enlace Reducido 110 x 63 mm PN16 HDPE GPA</t>
+  </si>
+  <si>
+    <t>Union Enlace Reducido 110 x 90 mm PN16 HDPE GPA</t>
+  </si>
+  <si>
+    <t>Enlace Tapon 110 mm PN16 HDPE GPA</t>
+  </si>
+  <si>
+    <t>Enlace Tapon 32 mm PN16 HDPE GPA</t>
+  </si>
+  <si>
+    <t>Enlace Codo 110 x 110 mm Bocas Iguales 90° VAE ITALY</t>
+  </si>
+  <si>
+    <t>Union Enlace Reducido 63 x 32 mm PN16 GPA</t>
+  </si>
+  <si>
+    <t>Union Enlace Reducido 32 x 20 mm VAE ITALY</t>
+  </si>
+  <si>
+    <t>Adaptador Enlace R/Macho 75 x 2" PN16 HDPE POELSAN</t>
+  </si>
+  <si>
+    <t>Union Enlace Reducido 65 x 63  mm PN16 HDPE FITSA</t>
+  </si>
+  <si>
+    <t>Enlace Tapon 50 mm PN16 HDPE GPA</t>
+  </si>
+  <si>
+    <t>Enlace Tapon 63 mm PN16 HDPE GPA</t>
+  </si>
+  <si>
+    <t>Cinta 17mm - 1.6Lt/H - 20CM - 8MIL- 1900M AKONA</t>
+  </si>
+  <si>
+    <t>Cinta 17mm - 1.6Lt/H - 30CM -10MIL- 1500M AKONA</t>
+  </si>
+  <si>
+    <t>Cinta 17mm - 2.3Lt/H - 20CM - 5MIL- 3200M AKONA</t>
+  </si>
+  <si>
+    <t>Manguera Duplex de 1" x (MT) (Flexible) NohaFlex</t>
+  </si>
+  <si>
+    <t>Manguera Duplex de 1" x 100mt. (Flexible) NohaFlex</t>
+  </si>
+  <si>
+    <t>Manguera Duplex de 3/4" x (MT) (Flexible) NohaFlex</t>
+  </si>
+  <si>
+    <t>Manguera Duplex de 3/4" x 100mt. (Rollo) (Flexible) NohaFlex</t>
+  </si>
+  <si>
+    <t>Manguera Duplex de 5/8" (MT) (Flexible) NohaFlex</t>
+  </si>
+  <si>
+    <t>Manguera Duplex de 5/8" x 100mt. (Flexible) NohaFlex</t>
+  </si>
+  <si>
+    <t>Manguera HDPE de 110mm (4") x 100mt AZUL PN 8</t>
+  </si>
+  <si>
+    <t>Manguera HDPE de 110mm (4") x 100mt PN 8</t>
+  </si>
+  <si>
+    <t>Manguera HDPE de 110mm (4") x 100mts AZUL PN 10</t>
+  </si>
+  <si>
+    <t>Manguera HDPE de 110mm (4") x 100mts PN 10</t>
+  </si>
+  <si>
+    <t>Manguera HDPE de 16 mm x 100mts PN 8</t>
+  </si>
+  <si>
+    <t>Manguera HDPE de 16 mm x 500mts PN 8</t>
+  </si>
+  <si>
+    <t>Manguera HDPE de 20mm (5/8") x 100mt PN 10</t>
+  </si>
+  <si>
+    <t>Manguera HDPE de 20mm (5/8") x 100mt PN 8</t>
+  </si>
+  <si>
+    <t>Manguera HDPE de 20mm x 100 AZUL PN 10</t>
+  </si>
+  <si>
+    <t>Manguera HDPE de 20mm x 100 AZUL PN 8</t>
+  </si>
+  <si>
+    <t>Manguera HDPE de 25mm (3/4") x 100 AZUL PN 10</t>
+  </si>
+  <si>
+    <t>Manguera HDPE de 25mm (3/4") x 100 AZUL PN 8</t>
+  </si>
+  <si>
+    <t>Manguera HDPE de 25mm (3/4") x 100mt PN 10</t>
+  </si>
+  <si>
+    <t>Manguera HDPE de 25mm (3/4") x 100mt PN 8</t>
+  </si>
+  <si>
+    <t>Manguera HDPE de 25mm (3/4") x ROLLO PN 8</t>
+  </si>
+  <si>
+    <t>Manguera HDPE de 32mm (1")  x Rollo PN 8</t>
+  </si>
+  <si>
+    <t>Manguera HDPE de 32mm (1") x 100 AZUL PN 10</t>
+  </si>
+  <si>
+    <t>Manguera HDPE de 32mm (1") x 100mt AZUL PN 12.5</t>
+  </si>
+  <si>
+    <t>Manguera HDPE de 32mm (1") x 100mts PN 10</t>
+  </si>
+  <si>
+    <t>Manguera HDPE de 32mm (1") x 100mts PN 12.5</t>
+  </si>
+  <si>
+    <t>Manguera HDPE de 32mm (1") x 100mts PN 8</t>
+  </si>
+  <si>
+    <t>Manguera HDPE de 32mm (1") x100 AZUL PN 8</t>
+  </si>
+  <si>
+    <t>Manguera HDPE de 50mm (1 1/2") x 100 PN 10</t>
+  </si>
+  <si>
+    <t>Manguera HDPE de 50mm (1 1/2") x 100 AZUL PN 10</t>
+  </si>
+  <si>
+    <t>Manguera HDPE de 50mm (1 1/2") x 100 AZUL PN 8</t>
+  </si>
+  <si>
+    <t>Manguera HDPE de 50mm (1 1/2") x 100 PN 8</t>
+  </si>
+  <si>
+    <t>Manguera HDPE de 63mm (2") x 100 Azul PN 10</t>
+  </si>
+  <si>
+    <t>Manguera HDPE de 63mm (2") x 100 Azul PN 8</t>
+  </si>
+  <si>
+    <t>Manguera HDPE de 63mm (2") x 100 PN 10</t>
+  </si>
+  <si>
+    <t>Manguera HDPE de 63mm (2") x 100mt PN 8</t>
+  </si>
+  <si>
+    <t>Manguera HDPE de 90mm (3") x 100mt AZUL PN 10</t>
+  </si>
+  <si>
+    <t>Manguera HDPE de 90mm (3") x 100mt AZUL PN 8</t>
+  </si>
+  <si>
+    <t>Manguera HDPE de 90mm (3") x 100mt PN 10</t>
+  </si>
+  <si>
+    <t>Manguera HDPE de 90mm (3") x 100mt PN 8</t>
+  </si>
+  <si>
+    <t>Manguera P/GLP 1/4" (Alta Presión) Negro x MT</t>
+  </si>
+  <si>
+    <t>Manguera P/GLP 3/8" (Alta Presión) Negro x MT</t>
+  </si>
+  <si>
+    <t>Manguera Premium P/GLP 3/8" x 100m Naranja "2M"</t>
+  </si>
+  <si>
+    <t>Manguera Premium P/GLP 3/8"xMT Naranja "2M"</t>
+  </si>
+  <si>
+    <t>Manguera Transparente de 1/2" (Mt)</t>
+  </si>
+  <si>
+    <t>Manguera Transparente de 1/2" x 100M (Rollo) p/Autom.</t>
+  </si>
+  <si>
+    <t>Manguera Transparente de 1/4" (Mt)</t>
+  </si>
+  <si>
+    <t>Manguera Transparente de 3/8" (Mt)</t>
+  </si>
+  <si>
+    <t>Manguera HDPE de 25mm (3/4") x 100 AZUL PN 12.5</t>
+  </si>
+  <si>
+    <t>Manguera HDPE de 32mm (1") x 100mts PN 8 C/F Verde</t>
+  </si>
+  <si>
+    <t>Manguera HDPE de 32mm (1") x 100mts PN 8 C/F Azul</t>
+  </si>
+  <si>
+    <t>Manguera HDPE de 50mm (1 1/2") x 100 PN 8 C/F Verde</t>
+  </si>
+  <si>
+    <t>Manguera HDPE de 50mm (1 1/2") x 100 PN 8 C/F Azul</t>
+  </si>
+  <si>
+    <t>Manguera HDPE de 63mm (2") x 100mt PN 8 C/F Verde</t>
+  </si>
+  <si>
+    <t>Manguera HDPE de 63mm (2") x 100mt PN 8 C/F Azul</t>
+  </si>
+  <si>
+    <t>Manguera Duplex de 1" x 100mt. (Flexible) PLASTICIR</t>
+  </si>
+  <si>
+    <t>Manguera Duplex de 3/4" x 100mt. (Flexible) PLASTICIR</t>
+  </si>
+  <si>
+    <t>Manguera Duplex de 5/8" x 100mt. (Flexible) PLASTICIR</t>
+  </si>
+  <si>
+    <t>Cinta de Goteo APOLLO C-6M 10CM 1.5L/H 3000M GREENPLAINS</t>
+  </si>
+  <si>
+    <t>Cinta de Goteo VIMI C-6M 20CM 2.2L/H 3000M GREENPLAINS</t>
+  </si>
+  <si>
+    <t>Manguera HDPE de 90mm (3") x 100mt AZUL</t>
+  </si>
+  <si>
+    <t>RA02</t>
+  </si>
+  <si>
+    <t>RA03</t>
+  </si>
+  <si>
+    <t>poelsan</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -464,7 +1560,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M188"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="25.28515625" customWidth="1"/>
@@ -739,7 +1835,3708 @@
         <v>14</v>
       </c>
     </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>35</v>
+      </c>
+      <c r="B10" t="s">
+        <v>212</v>
+      </c>
+      <c r="C10" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10" t="s">
+        <v>390</v>
+      </c>
+      <c r="G10" t="s">
+        <v>392</v>
+      </c>
+      <c r="H10">
+        <v>52.48</v>
+      </c>
+      <c r="I10">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B11" t="s">
+        <v>213</v>
+      </c>
+      <c r="C11" t="s">
+        <v>13</v>
+      </c>
+      <c r="E11" t="s">
+        <v>390</v>
+      </c>
+      <c r="G11" t="s">
+        <v>392</v>
+      </c>
+      <c r="H11">
+        <v>1.99</v>
+      </c>
+      <c r="I11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>37</v>
+      </c>
+      <c r="B12" t="s">
+        <v>214</v>
+      </c>
+      <c r="C12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E12" t="s">
+        <v>390</v>
+      </c>
+      <c r="G12" t="s">
+        <v>392</v>
+      </c>
+      <c r="H12">
+        <v>2.41</v>
+      </c>
+      <c r="I12">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>38</v>
+      </c>
+      <c r="B13" t="s">
+        <v>215</v>
+      </c>
+      <c r="C13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E13" t="s">
+        <v>390</v>
+      </c>
+      <c r="G13" t="s">
+        <v>392</v>
+      </c>
+      <c r="H13">
+        <v>2.54</v>
+      </c>
+      <c r="I13">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14" t="s">
+        <v>216</v>
+      </c>
+      <c r="C14" t="s">
+        <v>13</v>
+      </c>
+      <c r="E14" t="s">
+        <v>390</v>
+      </c>
+      <c r="G14" t="s">
+        <v>392</v>
+      </c>
+      <c r="H14">
+        <v>7.61</v>
+      </c>
+      <c r="I14">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>40</v>
+      </c>
+      <c r="B15" t="s">
+        <v>217</v>
+      </c>
+      <c r="C15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E15" t="s">
+        <v>390</v>
+      </c>
+      <c r="G15" t="s">
+        <v>392</v>
+      </c>
+      <c r="H15">
+        <v>9.94</v>
+      </c>
+      <c r="I15">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>41</v>
+      </c>
+      <c r="B16" t="s">
+        <v>218</v>
+      </c>
+      <c r="C16" t="s">
+        <v>13</v>
+      </c>
+      <c r="E16" t="s">
+        <v>390</v>
+      </c>
+      <c r="G16" t="s">
+        <v>392</v>
+      </c>
+      <c r="H16">
+        <v>33.36</v>
+      </c>
+      <c r="I16">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>42</v>
+      </c>
+      <c r="B17" t="s">
+        <v>219</v>
+      </c>
+      <c r="C17" t="s">
+        <v>13</v>
+      </c>
+      <c r="E17" t="s">
+        <v>390</v>
+      </c>
+      <c r="G17" t="s">
+        <v>392</v>
+      </c>
+      <c r="H17">
+        <v>51.65</v>
+      </c>
+      <c r="I17">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>43</v>
+      </c>
+      <c r="B18" t="s">
+        <v>220</v>
+      </c>
+      <c r="C18" t="s">
+        <v>13</v>
+      </c>
+      <c r="E18" t="s">
+        <v>390</v>
+      </c>
+      <c r="G18" t="s">
+        <v>392</v>
+      </c>
+      <c r="H18">
+        <v>1.57</v>
+      </c>
+      <c r="I18">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>44</v>
+      </c>
+      <c r="B19" t="s">
+        <v>221</v>
+      </c>
+      <c r="C19" t="s">
+        <v>13</v>
+      </c>
+      <c r="E19" t="s">
+        <v>390</v>
+      </c>
+      <c r="G19" t="s">
+        <v>392</v>
+      </c>
+      <c r="H19">
+        <v>2.06</v>
+      </c>
+      <c r="I19">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>45</v>
+      </c>
+      <c r="B20" t="s">
+        <v>222</v>
+      </c>
+      <c r="C20" t="s">
+        <v>13</v>
+      </c>
+      <c r="E20" t="s">
+        <v>390</v>
+      </c>
+      <c r="G20" t="s">
+        <v>392</v>
+      </c>
+      <c r="H20">
+        <v>2.12</v>
+      </c>
+      <c r="I20">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>46</v>
+      </c>
+      <c r="B21" t="s">
+        <v>223</v>
+      </c>
+      <c r="C21" t="s">
+        <v>13</v>
+      </c>
+      <c r="E21" t="s">
+        <v>390</v>
+      </c>
+      <c r="G21" t="s">
+        <v>392</v>
+      </c>
+      <c r="H21">
+        <v>6.94</v>
+      </c>
+      <c r="I21">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>47</v>
+      </c>
+      <c r="B22" t="s">
+        <v>224</v>
+      </c>
+      <c r="C22" t="s">
+        <v>13</v>
+      </c>
+      <c r="E22" t="s">
+        <v>390</v>
+      </c>
+      <c r="G22" t="s">
+        <v>392</v>
+      </c>
+      <c r="H22">
+        <v>8.51</v>
+      </c>
+      <c r="I22">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>48</v>
+      </c>
+      <c r="B23" t="s">
+        <v>225</v>
+      </c>
+      <c r="C23" t="s">
+        <v>13</v>
+      </c>
+      <c r="E23" t="s">
+        <v>390</v>
+      </c>
+      <c r="G23" t="s">
+        <v>392</v>
+      </c>
+      <c r="H23">
+        <v>25</v>
+      </c>
+      <c r="I23">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>49</v>
+      </c>
+      <c r="B24" t="s">
+        <v>226</v>
+      </c>
+      <c r="C24" t="s">
+        <v>13</v>
+      </c>
+      <c r="E24" t="s">
+        <v>390</v>
+      </c>
+      <c r="G24" t="s">
+        <v>392</v>
+      </c>
+      <c r="H24">
+        <v>24.95</v>
+      </c>
+      <c r="I24">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>50</v>
+      </c>
+      <c r="B25" t="s">
+        <v>227</v>
+      </c>
+      <c r="C25" t="s">
+        <v>13</v>
+      </c>
+      <c r="E25" t="s">
+        <v>390</v>
+      </c>
+      <c r="G25" t="s">
+        <v>392</v>
+      </c>
+      <c r="H25">
+        <v>60</v>
+      </c>
+      <c r="I25">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>51</v>
+      </c>
+      <c r="B26" t="s">
+        <v>228</v>
+      </c>
+      <c r="C26" t="s">
+        <v>13</v>
+      </c>
+      <c r="E26" t="s">
+        <v>390</v>
+      </c>
+      <c r="G26" t="s">
+        <v>392</v>
+      </c>
+      <c r="H26">
+        <v>94.77</v>
+      </c>
+      <c r="I26">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>52</v>
+      </c>
+      <c r="B27" t="s">
+        <v>229</v>
+      </c>
+      <c r="C27" t="s">
+        <v>13</v>
+      </c>
+      <c r="E27" t="s">
+        <v>390</v>
+      </c>
+      <c r="G27" t="s">
+        <v>392</v>
+      </c>
+      <c r="H27">
+        <v>3.04</v>
+      </c>
+      <c r="I27">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>53</v>
+      </c>
+      <c r="B28" t="s">
+        <v>230</v>
+      </c>
+      <c r="C28" t="s">
+        <v>13</v>
+      </c>
+      <c r="E28" t="s">
+        <v>390</v>
+      </c>
+      <c r="G28" t="s">
+        <v>392</v>
+      </c>
+      <c r="H28">
+        <v>4.3099999999999996</v>
+      </c>
+      <c r="I28">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>54</v>
+      </c>
+      <c r="B29" t="s">
+        <v>231</v>
+      </c>
+      <c r="C29" t="s">
+        <v>13</v>
+      </c>
+      <c r="E29" t="s">
+        <v>390</v>
+      </c>
+      <c r="G29" t="s">
+        <v>392</v>
+      </c>
+      <c r="H29">
+        <v>4.78</v>
+      </c>
+      <c r="I29">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>55</v>
+      </c>
+      <c r="B30" t="s">
+        <v>232</v>
+      </c>
+      <c r="C30" t="s">
+        <v>13</v>
+      </c>
+      <c r="E30" t="s">
+        <v>390</v>
+      </c>
+      <c r="G30" t="s">
+        <v>392</v>
+      </c>
+      <c r="H30">
+        <v>4.38</v>
+      </c>
+      <c r="I30">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>56</v>
+      </c>
+      <c r="B31" t="s">
+        <v>233</v>
+      </c>
+      <c r="C31" t="s">
+        <v>13</v>
+      </c>
+      <c r="E31" t="s">
+        <v>390</v>
+      </c>
+      <c r="G31" t="s">
+        <v>392</v>
+      </c>
+      <c r="H31">
+        <v>14.14</v>
+      </c>
+      <c r="I31">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>57</v>
+      </c>
+      <c r="B32" t="s">
+        <v>234</v>
+      </c>
+      <c r="C32" t="s">
+        <v>13</v>
+      </c>
+      <c r="E32" t="s">
+        <v>390</v>
+      </c>
+      <c r="G32" t="s">
+        <v>392</v>
+      </c>
+      <c r="H32">
+        <v>16.59</v>
+      </c>
+      <c r="I32">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>58</v>
+      </c>
+      <c r="B33" t="s">
+        <v>235</v>
+      </c>
+      <c r="C33" t="s">
+        <v>13</v>
+      </c>
+      <c r="E33" t="s">
+        <v>390</v>
+      </c>
+      <c r="G33" t="s">
+        <v>392</v>
+      </c>
+      <c r="H33">
+        <v>16.59</v>
+      </c>
+      <c r="I33">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>59</v>
+      </c>
+      <c r="B34" t="s">
+        <v>236</v>
+      </c>
+      <c r="C34" t="s">
+        <v>13</v>
+      </c>
+      <c r="E34" t="s">
+        <v>390</v>
+      </c>
+      <c r="G34" t="s">
+        <v>392</v>
+      </c>
+      <c r="H34">
+        <v>58</v>
+      </c>
+      <c r="I34">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>60</v>
+      </c>
+      <c r="B35" t="s">
+        <v>237</v>
+      </c>
+      <c r="C35" t="s">
+        <v>13</v>
+      </c>
+      <c r="E35" t="s">
+        <v>390</v>
+      </c>
+      <c r="G35" t="s">
+        <v>392</v>
+      </c>
+      <c r="H35">
+        <v>75.05</v>
+      </c>
+      <c r="I35">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>61</v>
+      </c>
+      <c r="B36" t="s">
+        <v>238</v>
+      </c>
+      <c r="C36" t="s">
+        <v>13</v>
+      </c>
+      <c r="E36" t="s">
+        <v>390</v>
+      </c>
+      <c r="G36" t="s">
+        <v>392</v>
+      </c>
+      <c r="H36">
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="I36">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>62</v>
+      </c>
+      <c r="B37" t="s">
+        <v>239</v>
+      </c>
+      <c r="C37" t="s">
+        <v>13</v>
+      </c>
+      <c r="E37" t="s">
+        <v>390</v>
+      </c>
+      <c r="G37" t="s">
+        <v>392</v>
+      </c>
+      <c r="H37">
+        <v>3.31</v>
+      </c>
+      <c r="I37">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>63</v>
+      </c>
+      <c r="B38" t="s">
+        <v>240</v>
+      </c>
+      <c r="C38" t="s">
+        <v>13</v>
+      </c>
+      <c r="E38" t="s">
+        <v>390</v>
+      </c>
+      <c r="G38" t="s">
+        <v>392</v>
+      </c>
+      <c r="H38">
+        <v>4.3099999999999996</v>
+      </c>
+      <c r="I38">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>64</v>
+      </c>
+      <c r="B39" t="s">
+        <v>241</v>
+      </c>
+      <c r="C39" t="s">
+        <v>13</v>
+      </c>
+      <c r="E39" t="s">
+        <v>390</v>
+      </c>
+      <c r="G39" t="s">
+        <v>392</v>
+      </c>
+      <c r="H39">
+        <v>4.3099999999999996</v>
+      </c>
+      <c r="I39">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>65</v>
+      </c>
+      <c r="B40" t="s">
+        <v>242</v>
+      </c>
+      <c r="C40" t="s">
+        <v>13</v>
+      </c>
+      <c r="E40" t="s">
+        <v>390</v>
+      </c>
+      <c r="G40" t="s">
+        <v>392</v>
+      </c>
+      <c r="H40">
+        <v>10.66</v>
+      </c>
+      <c r="I40">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>66</v>
+      </c>
+      <c r="B41" t="s">
+        <v>243</v>
+      </c>
+      <c r="C41" t="s">
+        <v>13</v>
+      </c>
+      <c r="E41" t="s">
+        <v>390</v>
+      </c>
+      <c r="G41" t="s">
+        <v>392</v>
+      </c>
+      <c r="H41">
+        <v>10.66</v>
+      </c>
+      <c r="I41">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>67</v>
+      </c>
+      <c r="B42" t="s">
+        <v>244</v>
+      </c>
+      <c r="C42" t="s">
+        <v>13</v>
+      </c>
+      <c r="E42" t="s">
+        <v>390</v>
+      </c>
+      <c r="G42" t="s">
+        <v>392</v>
+      </c>
+      <c r="H42">
+        <v>17.010000000000002</v>
+      </c>
+      <c r="I42">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>68</v>
+      </c>
+      <c r="B43" t="s">
+        <v>245</v>
+      </c>
+      <c r="C43" t="s">
+        <v>13</v>
+      </c>
+      <c r="E43" t="s">
+        <v>390</v>
+      </c>
+      <c r="G43" t="s">
+        <v>392</v>
+      </c>
+      <c r="H43">
+        <v>46.77</v>
+      </c>
+      <c r="I43">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>69</v>
+      </c>
+      <c r="B44" t="s">
+        <v>246</v>
+      </c>
+      <c r="C44" t="s">
+        <v>13</v>
+      </c>
+      <c r="E44" t="s">
+        <v>390</v>
+      </c>
+      <c r="G44" t="s">
+        <v>392</v>
+      </c>
+      <c r="H44">
+        <v>55.04</v>
+      </c>
+      <c r="I44">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>70</v>
+      </c>
+      <c r="B45" t="s">
+        <v>247</v>
+      </c>
+      <c r="C45" t="s">
+        <v>13</v>
+      </c>
+      <c r="E45" t="s">
+        <v>390</v>
+      </c>
+      <c r="G45" t="s">
+        <v>392</v>
+      </c>
+      <c r="H45">
+        <v>1.69</v>
+      </c>
+      <c r="I45">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>71</v>
+      </c>
+      <c r="B46" t="s">
+        <v>248</v>
+      </c>
+      <c r="C46" t="s">
+        <v>13</v>
+      </c>
+      <c r="E46" t="s">
+        <v>390</v>
+      </c>
+      <c r="G46" t="s">
+        <v>392</v>
+      </c>
+      <c r="H46">
+        <v>2.06</v>
+      </c>
+      <c r="I46">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>72</v>
+      </c>
+      <c r="B47" t="s">
+        <v>249</v>
+      </c>
+      <c r="C47" t="s">
+        <v>13</v>
+      </c>
+      <c r="E47" t="s">
+        <v>390</v>
+      </c>
+      <c r="G47" t="s">
+        <v>392</v>
+      </c>
+      <c r="H47">
+        <v>2.94</v>
+      </c>
+      <c r="I47">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>73</v>
+      </c>
+      <c r="B48" t="s">
+        <v>250</v>
+      </c>
+      <c r="C48" t="s">
+        <v>13</v>
+      </c>
+      <c r="E48" t="s">
+        <v>390</v>
+      </c>
+      <c r="G48" t="s">
+        <v>392</v>
+      </c>
+      <c r="H48">
+        <v>7.08</v>
+      </c>
+      <c r="I48">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>74</v>
+      </c>
+      <c r="B49" t="s">
+        <v>251</v>
+      </c>
+      <c r="C49" t="s">
+        <v>13</v>
+      </c>
+      <c r="E49" t="s">
+        <v>390</v>
+      </c>
+      <c r="G49" t="s">
+        <v>392</v>
+      </c>
+      <c r="H49">
+        <v>11.97</v>
+      </c>
+      <c r="I49">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>75</v>
+      </c>
+      <c r="B50" t="s">
+        <v>252</v>
+      </c>
+      <c r="C50" t="s">
+        <v>13</v>
+      </c>
+      <c r="E50" t="s">
+        <v>390</v>
+      </c>
+      <c r="G50" t="s">
+        <v>392</v>
+      </c>
+      <c r="H50">
+        <v>32.630000000000003</v>
+      </c>
+      <c r="I50">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>76</v>
+      </c>
+      <c r="B51" t="s">
+        <v>253</v>
+      </c>
+      <c r="C51" t="s">
+        <v>13</v>
+      </c>
+      <c r="E51" t="s">
+        <v>390</v>
+      </c>
+      <c r="H51">
+        <v>0.85</v>
+      </c>
+      <c r="I51">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>77</v>
+      </c>
+      <c r="B52" t="s">
+        <v>254</v>
+      </c>
+      <c r="C52" t="s">
+        <v>13</v>
+      </c>
+      <c r="E52" t="s">
+        <v>390</v>
+      </c>
+      <c r="H52">
+        <v>1</v>
+      </c>
+      <c r="I52">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>78</v>
+      </c>
+      <c r="B53" t="s">
+        <v>255</v>
+      </c>
+      <c r="C53" t="s">
+        <v>13</v>
+      </c>
+      <c r="E53" t="s">
+        <v>390</v>
+      </c>
+      <c r="H53">
+        <v>2.8</v>
+      </c>
+      <c r="I53">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>79</v>
+      </c>
+      <c r="B54" t="s">
+        <v>256</v>
+      </c>
+      <c r="C54" t="s">
+        <v>13</v>
+      </c>
+      <c r="E54" t="s">
+        <v>390</v>
+      </c>
+      <c r="H54">
+        <v>2.8</v>
+      </c>
+      <c r="I54">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>80</v>
+      </c>
+      <c r="B55" t="s">
+        <v>30</v>
+      </c>
+      <c r="C55" t="s">
+        <v>13</v>
+      </c>
+      <c r="E55" t="s">
+        <v>390</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>81</v>
+      </c>
+      <c r="B56" t="s">
+        <v>257</v>
+      </c>
+      <c r="C56" t="s">
+        <v>13</v>
+      </c>
+      <c r="E56" t="s">
+        <v>390</v>
+      </c>
+      <c r="H56">
+        <v>123.55</v>
+      </c>
+      <c r="I56">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>82</v>
+      </c>
+      <c r="B57" t="s">
+        <v>258</v>
+      </c>
+      <c r="C57" t="s">
+        <v>13</v>
+      </c>
+      <c r="E57" t="s">
+        <v>390</v>
+      </c>
+      <c r="H57">
+        <v>95</v>
+      </c>
+      <c r="I57">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>83</v>
+      </c>
+      <c r="B58" t="s">
+        <v>259</v>
+      </c>
+      <c r="C58" t="s">
+        <v>13</v>
+      </c>
+      <c r="E58" t="s">
+        <v>390</v>
+      </c>
+      <c r="H58">
+        <v>4.8</v>
+      </c>
+      <c r="I58">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>84</v>
+      </c>
+      <c r="B59" t="s">
+        <v>260</v>
+      </c>
+      <c r="C59" t="s">
+        <v>13</v>
+      </c>
+      <c r="E59" t="s">
+        <v>390</v>
+      </c>
+      <c r="H59">
+        <v>5.43</v>
+      </c>
+      <c r="I59">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>85</v>
+      </c>
+      <c r="B60" t="s">
+        <v>261</v>
+      </c>
+      <c r="C60" t="s">
+        <v>13</v>
+      </c>
+      <c r="E60" t="s">
+        <v>390</v>
+      </c>
+      <c r="H60">
+        <v>7.39</v>
+      </c>
+      <c r="I60">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>86</v>
+      </c>
+      <c r="B61" t="s">
+        <v>262</v>
+      </c>
+      <c r="C61" t="s">
+        <v>13</v>
+      </c>
+      <c r="E61" t="s">
+        <v>390</v>
+      </c>
+      <c r="H61">
+        <v>14</v>
+      </c>
+      <c r="I61">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>87</v>
+      </c>
+      <c r="B62" t="s">
+        <v>263</v>
+      </c>
+      <c r="C62" t="s">
+        <v>13</v>
+      </c>
+      <c r="E62" t="s">
+        <v>390</v>
+      </c>
+      <c r="H62">
+        <v>14</v>
+      </c>
+      <c r="I62">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>88</v>
+      </c>
+      <c r="B63" t="s">
+        <v>264</v>
+      </c>
+      <c r="C63" t="s">
+        <v>13</v>
+      </c>
+      <c r="E63" t="s">
+        <v>390</v>
+      </c>
+      <c r="H63">
+        <v>18.260000000000002</v>
+      </c>
+      <c r="I63">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>89</v>
+      </c>
+      <c r="B64" t="s">
+        <v>265</v>
+      </c>
+      <c r="C64" t="s">
+        <v>13</v>
+      </c>
+      <c r="E64" t="s">
+        <v>390</v>
+      </c>
+      <c r="H64">
+        <v>23.98</v>
+      </c>
+      <c r="I64">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>90</v>
+      </c>
+      <c r="B65" t="s">
+        <v>266</v>
+      </c>
+      <c r="C65" t="s">
+        <v>13</v>
+      </c>
+      <c r="E65" t="s">
+        <v>390</v>
+      </c>
+      <c r="H65">
+        <v>23.98</v>
+      </c>
+      <c r="I65">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>91</v>
+      </c>
+      <c r="B66" t="s">
+        <v>267</v>
+      </c>
+      <c r="C66" t="s">
+        <v>13</v>
+      </c>
+      <c r="E66" t="s">
+        <v>390</v>
+      </c>
+      <c r="H66">
+        <v>78.31</v>
+      </c>
+      <c r="I66">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>92</v>
+      </c>
+      <c r="B67" t="s">
+        <v>268</v>
+      </c>
+      <c r="C67" t="s">
+        <v>13</v>
+      </c>
+      <c r="E67" t="s">
+        <v>390</v>
+      </c>
+      <c r="H67">
+        <v>117.83</v>
+      </c>
+      <c r="I67">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>93</v>
+      </c>
+      <c r="B68" t="s">
+        <v>269</v>
+      </c>
+      <c r="C68" t="s">
+        <v>13</v>
+      </c>
+      <c r="E68" t="s">
+        <v>390</v>
+      </c>
+      <c r="H68">
+        <v>3.64</v>
+      </c>
+      <c r="I68">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>94</v>
+      </c>
+      <c r="B69" t="s">
+        <v>270</v>
+      </c>
+      <c r="C69" t="s">
+        <v>13</v>
+      </c>
+      <c r="E69" t="s">
+        <v>390</v>
+      </c>
+      <c r="H69">
+        <v>5.22</v>
+      </c>
+      <c r="I69">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>95</v>
+      </c>
+      <c r="B70" t="s">
+        <v>271</v>
+      </c>
+      <c r="C70" t="s">
+        <v>13</v>
+      </c>
+      <c r="E70" t="s">
+        <v>390</v>
+      </c>
+      <c r="H70">
+        <v>4.3</v>
+      </c>
+      <c r="I70">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>96</v>
+      </c>
+      <c r="B71" t="s">
+        <v>272</v>
+      </c>
+      <c r="C71" t="s">
+        <v>13</v>
+      </c>
+      <c r="E71" t="s">
+        <v>390</v>
+      </c>
+      <c r="H71">
+        <v>5</v>
+      </c>
+      <c r="I71">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>97</v>
+      </c>
+      <c r="B72" t="s">
+        <v>273</v>
+      </c>
+      <c r="C72" t="s">
+        <v>13</v>
+      </c>
+      <c r="E72" t="s">
+        <v>390</v>
+      </c>
+      <c r="H72">
+        <v>6.94</v>
+      </c>
+      <c r="I72">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>98</v>
+      </c>
+      <c r="B73" t="s">
+        <v>274</v>
+      </c>
+      <c r="C73" t="s">
+        <v>13</v>
+      </c>
+      <c r="E73" t="s">
+        <v>390</v>
+      </c>
+      <c r="H73">
+        <v>6.94</v>
+      </c>
+      <c r="I73">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>99</v>
+      </c>
+      <c r="B74" t="s">
+        <v>275</v>
+      </c>
+      <c r="C74" t="s">
+        <v>13</v>
+      </c>
+      <c r="E74" t="s">
+        <v>390</v>
+      </c>
+      <c r="H74">
+        <v>13</v>
+      </c>
+      <c r="I74">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>100</v>
+      </c>
+      <c r="B75" t="s">
+        <v>276</v>
+      </c>
+      <c r="C75" t="s">
+        <v>13</v>
+      </c>
+      <c r="E75" t="s">
+        <v>390</v>
+      </c>
+      <c r="H75">
+        <v>15.76</v>
+      </c>
+      <c r="I75">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>101</v>
+      </c>
+      <c r="B76" t="s">
+        <v>277</v>
+      </c>
+      <c r="C76" t="s">
+        <v>13</v>
+      </c>
+      <c r="E76" t="s">
+        <v>390</v>
+      </c>
+      <c r="H76">
+        <v>25.4</v>
+      </c>
+      <c r="I76">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>102</v>
+      </c>
+      <c r="B77" t="s">
+        <v>278</v>
+      </c>
+      <c r="C77" t="s">
+        <v>13</v>
+      </c>
+      <c r="E77" t="s">
+        <v>390</v>
+      </c>
+      <c r="H77">
+        <v>76.13</v>
+      </c>
+      <c r="I77">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>103</v>
+      </c>
+      <c r="B78" t="s">
+        <v>279</v>
+      </c>
+      <c r="C78" t="s">
+        <v>13</v>
+      </c>
+      <c r="E78" t="s">
+        <v>390</v>
+      </c>
+      <c r="H78">
+        <v>109.26</v>
+      </c>
+      <c r="I78">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>104</v>
+      </c>
+      <c r="B79" t="s">
+        <v>280</v>
+      </c>
+      <c r="C79" t="s">
+        <v>13</v>
+      </c>
+      <c r="E79" t="s">
+        <v>390</v>
+      </c>
+      <c r="H79">
+        <v>115.54</v>
+      </c>
+      <c r="I79">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>105</v>
+      </c>
+      <c r="B80" t="s">
+        <v>281</v>
+      </c>
+      <c r="C80" t="s">
+        <v>13</v>
+      </c>
+      <c r="E80" t="s">
+        <v>390</v>
+      </c>
+      <c r="H80">
+        <v>6.3</v>
+      </c>
+      <c r="I80">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>106</v>
+      </c>
+      <c r="B81" t="s">
+        <v>282</v>
+      </c>
+      <c r="C81" t="s">
+        <v>13</v>
+      </c>
+      <c r="E81" t="s">
+        <v>390</v>
+      </c>
+      <c r="H81">
+        <v>7.57</v>
+      </c>
+      <c r="I81">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>107</v>
+      </c>
+      <c r="B82" t="s">
+        <v>283</v>
+      </c>
+      <c r="C82" t="s">
+        <v>13</v>
+      </c>
+      <c r="E82" t="s">
+        <v>390</v>
+      </c>
+      <c r="H82">
+        <v>18.3</v>
+      </c>
+      <c r="I82">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>108</v>
+      </c>
+      <c r="B83" t="s">
+        <v>284</v>
+      </c>
+      <c r="C83" t="s">
+        <v>13</v>
+      </c>
+      <c r="E83" t="s">
+        <v>390</v>
+      </c>
+      <c r="H83">
+        <v>18</v>
+      </c>
+      <c r="I83">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>109</v>
+      </c>
+      <c r="B84" t="s">
+        <v>285</v>
+      </c>
+      <c r="C84" t="s">
+        <v>13</v>
+      </c>
+      <c r="E84" t="s">
+        <v>390</v>
+      </c>
+      <c r="H84">
+        <v>25.25</v>
+      </c>
+      <c r="I84">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>110</v>
+      </c>
+      <c r="B85" t="s">
+        <v>286</v>
+      </c>
+      <c r="C85" t="s">
+        <v>13</v>
+      </c>
+      <c r="E85" t="s">
+        <v>390</v>
+      </c>
+      <c r="H85">
+        <v>19</v>
+      </c>
+      <c r="I85">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>111</v>
+      </c>
+      <c r="B86" t="s">
+        <v>287</v>
+      </c>
+      <c r="C86" t="s">
+        <v>13</v>
+      </c>
+      <c r="E86" t="s">
+        <v>390</v>
+      </c>
+      <c r="H86">
+        <v>28.35</v>
+      </c>
+      <c r="I86">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>112</v>
+      </c>
+      <c r="B87" t="s">
+        <v>288</v>
+      </c>
+      <c r="C87" t="s">
+        <v>13</v>
+      </c>
+      <c r="E87" t="s">
+        <v>390</v>
+      </c>
+      <c r="H87">
+        <v>71.12</v>
+      </c>
+      <c r="I87">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>113</v>
+      </c>
+      <c r="B88" t="s">
+        <v>289</v>
+      </c>
+      <c r="C88" t="s">
+        <v>13</v>
+      </c>
+      <c r="E88" t="s">
+        <v>390</v>
+      </c>
+      <c r="H88">
+        <v>52</v>
+      </c>
+      <c r="I88">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>114</v>
+      </c>
+      <c r="B89" t="s">
+        <v>290</v>
+      </c>
+      <c r="C89" t="s">
+        <v>13</v>
+      </c>
+      <c r="E89" t="s">
+        <v>390</v>
+      </c>
+      <c r="H89">
+        <v>62.46</v>
+      </c>
+      <c r="I89">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>115</v>
+      </c>
+      <c r="B90" t="s">
+        <v>291</v>
+      </c>
+      <c r="C90" t="s">
+        <v>13</v>
+      </c>
+      <c r="E90" t="s">
+        <v>390</v>
+      </c>
+      <c r="H90">
+        <v>2.02</v>
+      </c>
+      <c r="I90">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>116</v>
+      </c>
+      <c r="B91" t="s">
+        <v>292</v>
+      </c>
+      <c r="C91" t="s">
+        <v>13</v>
+      </c>
+      <c r="E91" t="s">
+        <v>390</v>
+      </c>
+      <c r="H91">
+        <v>2.89</v>
+      </c>
+      <c r="I91">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>117</v>
+      </c>
+      <c r="B92" t="s">
+        <v>293</v>
+      </c>
+      <c r="C92" t="s">
+        <v>13</v>
+      </c>
+      <c r="E92" t="s">
+        <v>390</v>
+      </c>
+      <c r="H92">
+        <v>3.26</v>
+      </c>
+      <c r="I92">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>118</v>
+      </c>
+      <c r="B93" t="s">
+        <v>294</v>
+      </c>
+      <c r="C93" t="s">
+        <v>13</v>
+      </c>
+      <c r="E93" t="s">
+        <v>390</v>
+      </c>
+      <c r="H93">
+        <v>9.69</v>
+      </c>
+      <c r="I93">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>119</v>
+      </c>
+      <c r="B94" t="s">
+        <v>295</v>
+      </c>
+      <c r="C94" t="s">
+        <v>13</v>
+      </c>
+      <c r="E94" t="s">
+        <v>390</v>
+      </c>
+      <c r="H94">
+        <v>5.85</v>
+      </c>
+      <c r="I94">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>120</v>
+      </c>
+      <c r="B95" t="s">
+        <v>296</v>
+      </c>
+      <c r="C95" t="s">
+        <v>13</v>
+      </c>
+      <c r="E95" t="s">
+        <v>390</v>
+      </c>
+      <c r="H95">
+        <v>13.38</v>
+      </c>
+      <c r="I95">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>121</v>
+      </c>
+      <c r="B96" t="s">
+        <v>297</v>
+      </c>
+      <c r="C96" t="s">
+        <v>13</v>
+      </c>
+      <c r="E96" t="s">
+        <v>390</v>
+      </c>
+      <c r="H96">
+        <v>28</v>
+      </c>
+      <c r="I96">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>122</v>
+      </c>
+      <c r="B97" t="s">
+        <v>298</v>
+      </c>
+      <c r="C97" t="s">
+        <v>13</v>
+      </c>
+      <c r="E97" t="s">
+        <v>390</v>
+      </c>
+      <c r="H97">
+        <v>41.3</v>
+      </c>
+      <c r="I97">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>123</v>
+      </c>
+      <c r="B98" t="s">
+        <v>299</v>
+      </c>
+      <c r="C98" t="s">
+        <v>13</v>
+      </c>
+      <c r="E98" t="s">
+        <v>390</v>
+      </c>
+      <c r="H98">
+        <v>63.09</v>
+      </c>
+      <c r="I98">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>124</v>
+      </c>
+      <c r="B99" t="s">
+        <v>300</v>
+      </c>
+      <c r="C99" t="s">
+        <v>13</v>
+      </c>
+      <c r="E99" t="s">
+        <v>390</v>
+      </c>
+      <c r="H99">
+        <v>68.53</v>
+      </c>
+      <c r="I99">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>125</v>
+      </c>
+      <c r="B100" t="s">
+        <v>301</v>
+      </c>
+      <c r="C100" t="s">
+        <v>13</v>
+      </c>
+      <c r="E100" t="s">
+        <v>390</v>
+      </c>
+      <c r="H100">
+        <v>3.81</v>
+      </c>
+      <c r="I100">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>126</v>
+      </c>
+      <c r="B101" t="s">
+        <v>302</v>
+      </c>
+      <c r="C101" t="s">
+        <v>13</v>
+      </c>
+      <c r="E101" t="s">
+        <v>390</v>
+      </c>
+      <c r="H101">
+        <v>4.88</v>
+      </c>
+      <c r="I101">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>127</v>
+      </c>
+      <c r="B102" t="s">
+        <v>303</v>
+      </c>
+      <c r="C102" t="s">
+        <v>13</v>
+      </c>
+      <c r="E102" t="s">
+        <v>390</v>
+      </c>
+      <c r="H102">
+        <v>9.7799999999999994</v>
+      </c>
+      <c r="I102">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>128</v>
+      </c>
+      <c r="B103" t="s">
+        <v>304</v>
+      </c>
+      <c r="C103" t="s">
+        <v>13</v>
+      </c>
+      <c r="E103" t="s">
+        <v>390</v>
+      </c>
+      <c r="H103">
+        <v>15.01</v>
+      </c>
+      <c r="I103">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>129</v>
+      </c>
+      <c r="B104" t="s">
+        <v>305</v>
+      </c>
+      <c r="C104" t="s">
+        <v>13</v>
+      </c>
+      <c r="E104" t="s">
+        <v>390</v>
+      </c>
+      <c r="H104">
+        <v>16.309999999999999</v>
+      </c>
+      <c r="I104">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>130</v>
+      </c>
+      <c r="B105" t="s">
+        <v>306</v>
+      </c>
+      <c r="C105" t="s">
+        <v>13</v>
+      </c>
+      <c r="E105" t="s">
+        <v>390</v>
+      </c>
+      <c r="H105">
+        <v>30</v>
+      </c>
+      <c r="I105">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>131</v>
+      </c>
+      <c r="B106" t="s">
+        <v>307</v>
+      </c>
+      <c r="C106" t="s">
+        <v>13</v>
+      </c>
+      <c r="E106" t="s">
+        <v>390</v>
+      </c>
+      <c r="H106">
+        <v>40.78</v>
+      </c>
+      <c r="I106">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>132</v>
+      </c>
+      <c r="B107" t="s">
+        <v>308</v>
+      </c>
+      <c r="C107" t="s">
+        <v>13</v>
+      </c>
+      <c r="E107" t="s">
+        <v>390</v>
+      </c>
+      <c r="H107">
+        <v>40</v>
+      </c>
+      <c r="I107">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>133</v>
+      </c>
+      <c r="B108" t="s">
+        <v>309</v>
+      </c>
+      <c r="C108" t="s">
+        <v>13</v>
+      </c>
+      <c r="E108" t="s">
+        <v>390</v>
+      </c>
+      <c r="H108">
+        <v>27</v>
+      </c>
+      <c r="I108">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>134</v>
+      </c>
+      <c r="B109" t="s">
+        <v>310</v>
+      </c>
+      <c r="C109" t="s">
+        <v>13</v>
+      </c>
+      <c r="E109" t="s">
+        <v>390</v>
+      </c>
+      <c r="H109">
+        <v>30</v>
+      </c>
+      <c r="I109">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>135</v>
+      </c>
+      <c r="B110" t="s">
+        <v>311</v>
+      </c>
+      <c r="C110" t="s">
+        <v>13</v>
+      </c>
+      <c r="E110" t="s">
+        <v>390</v>
+      </c>
+      <c r="H110">
+        <v>7.61</v>
+      </c>
+      <c r="I110">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>136</v>
+      </c>
+      <c r="B111" t="s">
+        <v>312</v>
+      </c>
+      <c r="C111" t="s">
+        <v>13</v>
+      </c>
+      <c r="E111" t="s">
+        <v>390</v>
+      </c>
+      <c r="H111">
+        <v>2.41</v>
+      </c>
+      <c r="I111">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>137</v>
+      </c>
+      <c r="B112" t="s">
+        <v>313</v>
+      </c>
+      <c r="C112" t="s">
+        <v>13</v>
+      </c>
+      <c r="E112" t="s">
+        <v>390</v>
+      </c>
+      <c r="H112">
+        <v>0</v>
+      </c>
+      <c r="I112">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>138</v>
+      </c>
+      <c r="B113" t="s">
+        <v>314</v>
+      </c>
+      <c r="C113" t="s">
+        <v>13</v>
+      </c>
+      <c r="E113" t="s">
+        <v>390</v>
+      </c>
+      <c r="H113">
+        <v>0</v>
+      </c>
+      <c r="I113">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>139</v>
+      </c>
+      <c r="B114" t="s">
+        <v>315</v>
+      </c>
+      <c r="C114" t="s">
+        <v>13</v>
+      </c>
+      <c r="E114" t="s">
+        <v>390</v>
+      </c>
+      <c r="H114">
+        <v>52</v>
+      </c>
+      <c r="I114">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>140</v>
+      </c>
+      <c r="B115" t="s">
+        <v>316</v>
+      </c>
+      <c r="C115" t="s">
+        <v>13</v>
+      </c>
+      <c r="E115" t="s">
+        <v>390</v>
+      </c>
+      <c r="H115">
+        <v>55</v>
+      </c>
+      <c r="I115">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>141</v>
+      </c>
+      <c r="B116" t="s">
+        <v>317</v>
+      </c>
+      <c r="C116" t="s">
+        <v>13</v>
+      </c>
+      <c r="E116" t="s">
+        <v>390</v>
+      </c>
+      <c r="H116">
+        <v>39</v>
+      </c>
+      <c r="I116">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>142</v>
+      </c>
+      <c r="B117" t="s">
+        <v>318</v>
+      </c>
+      <c r="C117" t="s">
+        <v>13</v>
+      </c>
+      <c r="E117" t="s">
+        <v>390</v>
+      </c>
+      <c r="H117">
+        <v>2.4</v>
+      </c>
+      <c r="I117">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>143</v>
+      </c>
+      <c r="B118" t="s">
+        <v>319</v>
+      </c>
+      <c r="C118" t="s">
+        <v>13</v>
+      </c>
+      <c r="E118" t="s">
+        <v>390</v>
+      </c>
+      <c r="H118">
+        <v>52</v>
+      </c>
+      <c r="I118">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>144</v>
+      </c>
+      <c r="B119" t="s">
+        <v>320</v>
+      </c>
+      <c r="C119" t="s">
+        <v>13</v>
+      </c>
+      <c r="E119" t="s">
+        <v>390</v>
+      </c>
+      <c r="H119">
+        <v>15.01</v>
+      </c>
+      <c r="I119">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>145</v>
+      </c>
+      <c r="B120" t="s">
+        <v>321</v>
+      </c>
+      <c r="C120" t="s">
+        <v>13</v>
+      </c>
+      <c r="E120" t="s">
+        <v>390</v>
+      </c>
+      <c r="H120">
+        <v>4.88</v>
+      </c>
+      <c r="I120">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>146</v>
+      </c>
+      <c r="B121" t="s">
+        <v>322</v>
+      </c>
+      <c r="C121" t="s">
+        <v>13</v>
+      </c>
+      <c r="E121" t="s">
+        <v>390</v>
+      </c>
+      <c r="H121">
+        <v>25</v>
+      </c>
+      <c r="I121">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>147</v>
+      </c>
+      <c r="B122" t="s">
+        <v>323</v>
+      </c>
+      <c r="C122" t="s">
+        <v>13</v>
+      </c>
+      <c r="E122" t="s">
+        <v>390</v>
+      </c>
+      <c r="H122">
+        <v>15.01</v>
+      </c>
+      <c r="I122">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>141</v>
+      </c>
+      <c r="B123" t="s">
+        <v>324</v>
+      </c>
+      <c r="C123" t="s">
+        <v>13</v>
+      </c>
+      <c r="E123" t="s">
+        <v>390</v>
+      </c>
+      <c r="H123">
+        <v>39</v>
+      </c>
+      <c r="I123">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>141</v>
+      </c>
+      <c r="B124" t="s">
+        <v>325</v>
+      </c>
+      <c r="C124" t="s">
+        <v>13</v>
+      </c>
+      <c r="E124" t="s">
+        <v>390</v>
+      </c>
+      <c r="H124">
+        <v>39</v>
+      </c>
+      <c r="I124">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>148</v>
+      </c>
+      <c r="B125" t="s">
+        <v>326</v>
+      </c>
+      <c r="C125" t="s">
+        <v>13</v>
+      </c>
+      <c r="E125" t="s">
+        <v>391</v>
+      </c>
+      <c r="H125">
+        <v>327</v>
+      </c>
+      <c r="I125">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>149</v>
+      </c>
+      <c r="B126" t="s">
+        <v>327</v>
+      </c>
+      <c r="C126" t="s">
+        <v>13</v>
+      </c>
+      <c r="E126" t="s">
+        <v>391</v>
+      </c>
+      <c r="H126">
+        <v>0</v>
+      </c>
+      <c r="I126">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>150</v>
+      </c>
+      <c r="B127" t="s">
+        <v>328</v>
+      </c>
+      <c r="C127" t="s">
+        <v>13</v>
+      </c>
+      <c r="E127" t="s">
+        <v>391</v>
+      </c>
+      <c r="H127">
+        <v>420</v>
+      </c>
+      <c r="I127">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>151</v>
+      </c>
+      <c r="B128" t="s">
+        <v>329</v>
+      </c>
+      <c r="C128" t="s">
+        <v>13</v>
+      </c>
+      <c r="E128" t="s">
+        <v>391</v>
+      </c>
+      <c r="H128">
+        <v>0</v>
+      </c>
+      <c r="I128">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>152</v>
+      </c>
+      <c r="B129" t="s">
+        <v>330</v>
+      </c>
+      <c r="C129" t="s">
+        <v>13</v>
+      </c>
+      <c r="E129" t="s">
+        <v>391</v>
+      </c>
+      <c r="H129">
+        <v>0</v>
+      </c>
+      <c r="I129">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>153</v>
+      </c>
+      <c r="B130" t="s">
+        <v>331</v>
+      </c>
+      <c r="C130" t="s">
+        <v>13</v>
+      </c>
+      <c r="E130" t="s">
+        <v>391</v>
+      </c>
+      <c r="H130">
+        <v>0</v>
+      </c>
+      <c r="I130">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>154</v>
+      </c>
+      <c r="B131" t="s">
+        <v>332</v>
+      </c>
+      <c r="C131" t="s">
+        <v>13</v>
+      </c>
+      <c r="E131" t="s">
+        <v>391</v>
+      </c>
+      <c r="H131">
+        <v>0</v>
+      </c>
+      <c r="I131">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>155</v>
+      </c>
+      <c r="B132" t="s">
+        <v>333</v>
+      </c>
+      <c r="C132" t="s">
+        <v>13</v>
+      </c>
+      <c r="E132" t="s">
+        <v>391</v>
+      </c>
+      <c r="H132">
+        <v>0</v>
+      </c>
+      <c r="I132">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>156</v>
+      </c>
+      <c r="B133" t="s">
+        <v>334</v>
+      </c>
+      <c r="C133" t="s">
+        <v>13</v>
+      </c>
+      <c r="E133" t="s">
+        <v>391</v>
+      </c>
+      <c r="H133">
+        <v>0</v>
+      </c>
+      <c r="I133">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>157</v>
+      </c>
+      <c r="B134" t="s">
+        <v>335</v>
+      </c>
+      <c r="C134" t="s">
+        <v>13</v>
+      </c>
+      <c r="E134" t="s">
+        <v>391</v>
+      </c>
+      <c r="H134">
+        <v>0</v>
+      </c>
+      <c r="I134">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>158</v>
+      </c>
+      <c r="B135" t="s">
+        <v>336</v>
+      </c>
+      <c r="C135" t="s">
+        <v>13</v>
+      </c>
+      <c r="E135" t="s">
+        <v>391</v>
+      </c>
+      <c r="H135">
+        <v>1019.2</v>
+      </c>
+      <c r="I135">
+        <v>1350</v>
+      </c>
+    </row>
+    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>159</v>
+      </c>
+      <c r="B136" t="s">
+        <v>337</v>
+      </c>
+      <c r="C136" t="s">
+        <v>13</v>
+      </c>
+      <c r="E136" t="s">
+        <v>391</v>
+      </c>
+      <c r="H136">
+        <v>1450.8</v>
+      </c>
+      <c r="I136">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>160</v>
+      </c>
+      <c r="B137" t="s">
+        <v>338</v>
+      </c>
+      <c r="C137" t="s">
+        <v>13</v>
+      </c>
+      <c r="E137" t="s">
+        <v>391</v>
+      </c>
+      <c r="H137">
+        <v>1404</v>
+      </c>
+      <c r="I137">
+        <v>1650</v>
+      </c>
+    </row>
+    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>161</v>
+      </c>
+      <c r="B138" t="s">
+        <v>339</v>
+      </c>
+      <c r="C138" t="s">
+        <v>13</v>
+      </c>
+      <c r="E138" t="s">
+        <v>391</v>
+      </c>
+      <c r="H138">
+        <v>24.96</v>
+      </c>
+      <c r="I138">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>162</v>
+      </c>
+      <c r="B139" t="s">
+        <v>340</v>
+      </c>
+      <c r="C139" t="s">
+        <v>13</v>
+      </c>
+      <c r="E139" t="s">
+        <v>391</v>
+      </c>
+      <c r="H139">
+        <v>88.4</v>
+      </c>
+      <c r="I139">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>163</v>
+      </c>
+      <c r="B140" t="s">
+        <v>341</v>
+      </c>
+      <c r="C140" t="s">
+        <v>13</v>
+      </c>
+      <c r="E140" t="s">
+        <v>391</v>
+      </c>
+      <c r="H140">
+        <v>52</v>
+      </c>
+      <c r="I140">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>164</v>
+      </c>
+      <c r="B141" t="s">
+        <v>342</v>
+      </c>
+      <c r="C141" t="s">
+        <v>13</v>
+      </c>
+      <c r="E141" t="s">
+        <v>391</v>
+      </c>
+      <c r="H141">
+        <v>34.32</v>
+      </c>
+      <c r="I141">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>165</v>
+      </c>
+      <c r="B142" t="s">
+        <v>343</v>
+      </c>
+      <c r="C142" t="s">
+        <v>13</v>
+      </c>
+      <c r="E142" t="s">
+        <v>391</v>
+      </c>
+      <c r="H142">
+        <v>62.4</v>
+      </c>
+      <c r="I142">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>166</v>
+      </c>
+      <c r="B143" t="s">
+        <v>344</v>
+      </c>
+      <c r="C143" t="s">
+        <v>13</v>
+      </c>
+      <c r="E143" t="s">
+        <v>391</v>
+      </c>
+      <c r="H143">
+        <v>46.8</v>
+      </c>
+      <c r="I143">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>167</v>
+      </c>
+      <c r="B144" t="s">
+        <v>345</v>
+      </c>
+      <c r="C144" t="s">
+        <v>13</v>
+      </c>
+      <c r="E144" t="s">
+        <v>391</v>
+      </c>
+      <c r="H144">
+        <v>93.6</v>
+      </c>
+      <c r="I144">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>168</v>
+      </c>
+      <c r="B145" t="s">
+        <v>346</v>
+      </c>
+      <c r="C145" t="s">
+        <v>13</v>
+      </c>
+      <c r="E145" t="s">
+        <v>391</v>
+      </c>
+      <c r="H145">
+        <v>62.4</v>
+      </c>
+      <c r="I145">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>169</v>
+      </c>
+      <c r="B146" t="s">
+        <v>347</v>
+      </c>
+      <c r="C146" t="s">
+        <v>13</v>
+      </c>
+      <c r="E146" t="s">
+        <v>391</v>
+      </c>
+      <c r="H146">
+        <v>67.599999999999994</v>
+      </c>
+      <c r="I146">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>170</v>
+      </c>
+      <c r="B147" t="s">
+        <v>348</v>
+      </c>
+      <c r="C147" t="s">
+        <v>13</v>
+      </c>
+      <c r="E147" t="s">
+        <v>391</v>
+      </c>
+      <c r="H147">
+        <v>46.8</v>
+      </c>
+      <c r="I147">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>171</v>
+      </c>
+      <c r="B148" t="s">
+        <v>349</v>
+      </c>
+      <c r="C148" t="s">
+        <v>13</v>
+      </c>
+      <c r="E148" t="s">
+        <v>391</v>
+      </c>
+      <c r="H148">
+        <v>44.72</v>
+      </c>
+      <c r="I148">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>172</v>
+      </c>
+      <c r="B149" t="s">
+        <v>350</v>
+      </c>
+      <c r="C149" t="s">
+        <v>13</v>
+      </c>
+      <c r="E149" t="s">
+        <v>391</v>
+      </c>
+      <c r="H149">
+        <v>62.4</v>
+      </c>
+      <c r="I149">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>173</v>
+      </c>
+      <c r="B150" t="s">
+        <v>351</v>
+      </c>
+      <c r="C150" t="s">
+        <v>13</v>
+      </c>
+      <c r="E150" t="s">
+        <v>391</v>
+      </c>
+      <c r="H150">
+        <v>135.19999999999999</v>
+      </c>
+      <c r="I150">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>174</v>
+      </c>
+      <c r="B151" t="s">
+        <v>352</v>
+      </c>
+      <c r="C151" t="s">
+        <v>13</v>
+      </c>
+      <c r="E151" t="s">
+        <v>391</v>
+      </c>
+      <c r="H151">
+        <v>145.6</v>
+      </c>
+      <c r="I151">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>175</v>
+      </c>
+      <c r="B152" t="s">
+        <v>353</v>
+      </c>
+      <c r="C152" t="s">
+        <v>13</v>
+      </c>
+      <c r="E152" t="s">
+        <v>391</v>
+      </c>
+      <c r="H152">
+        <v>93.6</v>
+      </c>
+      <c r="I152">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>176</v>
+      </c>
+      <c r="B153" t="s">
+        <v>354</v>
+      </c>
+      <c r="C153" t="s">
+        <v>13</v>
+      </c>
+      <c r="E153" t="s">
+        <v>391</v>
+      </c>
+      <c r="H153">
+        <v>140.4</v>
+      </c>
+      <c r="I153">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>177</v>
+      </c>
+      <c r="B154" t="s">
+        <v>355</v>
+      </c>
+      <c r="C154" t="s">
+        <v>13</v>
+      </c>
+      <c r="E154" t="s">
+        <v>391</v>
+      </c>
+      <c r="H154">
+        <v>67.599999999999994</v>
+      </c>
+      <c r="I154">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>178</v>
+      </c>
+      <c r="B155" t="s">
+        <v>356</v>
+      </c>
+      <c r="C155" t="s">
+        <v>13</v>
+      </c>
+      <c r="E155" t="s">
+        <v>391</v>
+      </c>
+      <c r="H155">
+        <v>104</v>
+      </c>
+      <c r="I155">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>179</v>
+      </c>
+      <c r="B156" t="s">
+        <v>357</v>
+      </c>
+      <c r="C156" t="s">
+        <v>13</v>
+      </c>
+      <c r="E156" t="s">
+        <v>391</v>
+      </c>
+      <c r="H156">
+        <v>228.8</v>
+      </c>
+      <c r="I156">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>180</v>
+      </c>
+      <c r="B157" t="s">
+        <v>358</v>
+      </c>
+      <c r="C157" t="s">
+        <v>13</v>
+      </c>
+      <c r="E157" t="s">
+        <v>391</v>
+      </c>
+      <c r="H157">
+        <v>312</v>
+      </c>
+      <c r="I157">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>181</v>
+      </c>
+      <c r="B158" t="s">
+        <v>359</v>
+      </c>
+      <c r="C158" t="s">
+        <v>13</v>
+      </c>
+      <c r="E158" t="s">
+        <v>391</v>
+      </c>
+      <c r="H158">
+        <v>239.2</v>
+      </c>
+      <c r="I158">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>182</v>
+      </c>
+      <c r="B159" t="s">
+        <v>360</v>
+      </c>
+      <c r="C159" t="s">
+        <v>13</v>
+      </c>
+      <c r="E159" t="s">
+        <v>391</v>
+      </c>
+      <c r="H159">
+        <v>145.6</v>
+      </c>
+      <c r="I159">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>183</v>
+      </c>
+      <c r="B160" t="s">
+        <v>361</v>
+      </c>
+      <c r="C160" t="s">
+        <v>13</v>
+      </c>
+      <c r="E160" t="s">
+        <v>391</v>
+      </c>
+      <c r="H160">
+        <v>468</v>
+      </c>
+      <c r="I160">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>184</v>
+      </c>
+      <c r="B161" t="s">
+        <v>362</v>
+      </c>
+      <c r="C161" t="s">
+        <v>13</v>
+      </c>
+      <c r="E161" t="s">
+        <v>391</v>
+      </c>
+      <c r="H161">
+        <v>358.8</v>
+      </c>
+      <c r="I161">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>185</v>
+      </c>
+      <c r="B162" t="s">
+        <v>363</v>
+      </c>
+      <c r="C162" t="s">
+        <v>13</v>
+      </c>
+      <c r="E162" t="s">
+        <v>391</v>
+      </c>
+      <c r="H162">
+        <v>378.56</v>
+      </c>
+      <c r="I162">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>186</v>
+      </c>
+      <c r="B163" t="s">
+        <v>364</v>
+      </c>
+      <c r="C163" t="s">
+        <v>13</v>
+      </c>
+      <c r="E163" t="s">
+        <v>391</v>
+      </c>
+      <c r="H163">
+        <v>232.96</v>
+      </c>
+      <c r="I163">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
+        <v>187</v>
+      </c>
+      <c r="B164" t="s">
+        <v>365</v>
+      </c>
+      <c r="C164" t="s">
+        <v>13</v>
+      </c>
+      <c r="E164" t="s">
+        <v>391</v>
+      </c>
+      <c r="H164">
+        <v>1144</v>
+      </c>
+      <c r="I164">
+        <v>1284</v>
+      </c>
+    </row>
+    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>188</v>
+      </c>
+      <c r="B165" t="s">
+        <v>366</v>
+      </c>
+      <c r="C165" t="s">
+        <v>13</v>
+      </c>
+      <c r="E165" t="s">
+        <v>391</v>
+      </c>
+      <c r="H165">
+        <v>832</v>
+      </c>
+      <c r="I165">
+        <v>965</v>
+      </c>
+    </row>
+    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
+        <v>189</v>
+      </c>
+      <c r="B166" t="s">
+        <v>367</v>
+      </c>
+      <c r="C166" t="s">
+        <v>13</v>
+      </c>
+      <c r="E166" t="s">
+        <v>391</v>
+      </c>
+      <c r="H166">
+        <v>884</v>
+      </c>
+      <c r="I166">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>190</v>
+      </c>
+      <c r="B167" t="s">
+        <v>368</v>
+      </c>
+      <c r="C167" t="s">
+        <v>13</v>
+      </c>
+      <c r="E167" t="s">
+        <v>391</v>
+      </c>
+      <c r="H167">
+        <v>613.6</v>
+      </c>
+      <c r="I167">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>191</v>
+      </c>
+      <c r="B168" t="s">
+        <v>369</v>
+      </c>
+      <c r="C168" t="s">
+        <v>13</v>
+      </c>
+      <c r="E168" t="s">
+        <v>391</v>
+      </c>
+      <c r="H168">
+        <v>0</v>
+      </c>
+      <c r="I168">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
+        <v>192</v>
+      </c>
+      <c r="B169" t="s">
+        <v>370</v>
+      </c>
+      <c r="C169" t="s">
+        <v>13</v>
+      </c>
+      <c r="E169" t="s">
+        <v>391</v>
+      </c>
+      <c r="H169">
+        <v>0</v>
+      </c>
+      <c r="I169">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
+        <v>193</v>
+      </c>
+      <c r="B170" t="s">
+        <v>371</v>
+      </c>
+      <c r="C170" t="s">
+        <v>13</v>
+      </c>
+      <c r="E170" t="s">
+        <v>391</v>
+      </c>
+      <c r="H170">
+        <v>0</v>
+      </c>
+      <c r="I170">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
+        <v>194</v>
+      </c>
+      <c r="B171" t="s">
+        <v>372</v>
+      </c>
+      <c r="C171" t="s">
+        <v>13</v>
+      </c>
+      <c r="E171" t="s">
+        <v>391</v>
+      </c>
+      <c r="H171">
+        <v>0</v>
+      </c>
+      <c r="I171">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
+        <v>195</v>
+      </c>
+      <c r="B172" t="s">
+        <v>373</v>
+      </c>
+      <c r="C172" t="s">
+        <v>13</v>
+      </c>
+      <c r="E172" t="s">
+        <v>391</v>
+      </c>
+      <c r="H172">
+        <v>0</v>
+      </c>
+      <c r="I172">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
+        <v>196</v>
+      </c>
+      <c r="B173" t="s">
+        <v>374</v>
+      </c>
+      <c r="C173" t="s">
+        <v>13</v>
+      </c>
+      <c r="E173" t="s">
+        <v>391</v>
+      </c>
+      <c r="H173">
+        <v>0</v>
+      </c>
+      <c r="I173">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
+        <v>197</v>
+      </c>
+      <c r="B174" t="s">
+        <v>375</v>
+      </c>
+      <c r="C174" t="s">
+        <v>13</v>
+      </c>
+      <c r="E174" t="s">
+        <v>391</v>
+      </c>
+      <c r="H174">
+        <v>0</v>
+      </c>
+      <c r="I174">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="175" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
+        <v>198</v>
+      </c>
+      <c r="B175" t="s">
+        <v>376</v>
+      </c>
+      <c r="C175" t="s">
+        <v>13</v>
+      </c>
+      <c r="E175" t="s">
+        <v>391</v>
+      </c>
+      <c r="H175">
+        <v>0</v>
+      </c>
+      <c r="I175">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A176" t="s">
+        <v>199</v>
+      </c>
+      <c r="B176" t="s">
+        <v>377</v>
+      </c>
+      <c r="C176" t="s">
+        <v>13</v>
+      </c>
+      <c r="E176" t="s">
+        <v>391</v>
+      </c>
+      <c r="H176">
+        <v>93.6</v>
+      </c>
+      <c r="I176">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="177" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A177" t="s">
+        <v>200</v>
+      </c>
+      <c r="B177" t="s">
+        <v>378</v>
+      </c>
+      <c r="C177" t="s">
+        <v>13</v>
+      </c>
+      <c r="E177" t="s">
+        <v>391</v>
+      </c>
+      <c r="H177">
+        <v>67.599999999999994</v>
+      </c>
+      <c r="I177">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="178" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A178" t="s">
+        <v>201</v>
+      </c>
+      <c r="B178" t="s">
+        <v>379</v>
+      </c>
+      <c r="C178" t="s">
+        <v>13</v>
+      </c>
+      <c r="E178" t="s">
+        <v>391</v>
+      </c>
+      <c r="H178">
+        <v>67.599999999999994</v>
+      </c>
+      <c r="I178">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="179" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A179" t="s">
+        <v>202</v>
+      </c>
+      <c r="B179" t="s">
+        <v>380</v>
+      </c>
+      <c r="C179" t="s">
+        <v>13</v>
+      </c>
+      <c r="E179" t="s">
+        <v>391</v>
+      </c>
+      <c r="H179">
+        <v>145.6</v>
+      </c>
+      <c r="I179">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="180" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A180" t="s">
+        <v>203</v>
+      </c>
+      <c r="B180" t="s">
+        <v>381</v>
+      </c>
+      <c r="C180" t="s">
+        <v>13</v>
+      </c>
+      <c r="E180" t="s">
+        <v>391</v>
+      </c>
+      <c r="H180">
+        <v>145.6</v>
+      </c>
+      <c r="I180">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="181" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A181" t="s">
+        <v>204</v>
+      </c>
+      <c r="B181" t="s">
+        <v>382</v>
+      </c>
+      <c r="C181" t="s">
+        <v>13</v>
+      </c>
+      <c r="E181" t="s">
+        <v>391</v>
+      </c>
+      <c r="H181">
+        <v>232.96</v>
+      </c>
+      <c r="I181">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="182" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A182" t="s">
+        <v>205</v>
+      </c>
+      <c r="B182" t="s">
+        <v>383</v>
+      </c>
+      <c r="C182" t="s">
+        <v>13</v>
+      </c>
+      <c r="E182" t="s">
+        <v>391</v>
+      </c>
+      <c r="H182">
+        <v>232.96</v>
+      </c>
+      <c r="I182">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="183" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A183" t="s">
+        <v>206</v>
+      </c>
+      <c r="B183" t="s">
+        <v>384</v>
+      </c>
+      <c r="C183" t="s">
+        <v>13</v>
+      </c>
+      <c r="E183" t="s">
+        <v>391</v>
+      </c>
+      <c r="H183">
+        <v>0</v>
+      </c>
+      <c r="I183">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="184" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A184" t="s">
+        <v>207</v>
+      </c>
+      <c r="B184" t="s">
+        <v>385</v>
+      </c>
+      <c r="C184" t="s">
+        <v>13</v>
+      </c>
+      <c r="E184" t="s">
+        <v>391</v>
+      </c>
+      <c r="H184">
+        <v>0</v>
+      </c>
+      <c r="I184">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="185" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A185" t="s">
+        <v>208</v>
+      </c>
+      <c r="B185" t="s">
+        <v>386</v>
+      </c>
+      <c r="C185" t="s">
+        <v>13</v>
+      </c>
+      <c r="E185" t="s">
+        <v>391</v>
+      </c>
+      <c r="H185">
+        <v>0</v>
+      </c>
+      <c r="I185">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="186" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A186" t="s">
+        <v>209</v>
+      </c>
+      <c r="B186" t="s">
+        <v>387</v>
+      </c>
+      <c r="C186" t="s">
+        <v>13</v>
+      </c>
+      <c r="E186" t="s">
+        <v>391</v>
+      </c>
+      <c r="H186">
+        <v>470</v>
+      </c>
+      <c r="I186">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="187" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A187" t="s">
+        <v>210</v>
+      </c>
+      <c r="B187" t="s">
+        <v>388</v>
+      </c>
+      <c r="C187" t="s">
+        <v>13</v>
+      </c>
+      <c r="E187" t="s">
+        <v>391</v>
+      </c>
+      <c r="H187">
+        <v>390</v>
+      </c>
+      <c r="I187">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="188" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A188" t="s">
+        <v>211</v>
+      </c>
+      <c r="B188" t="s">
+        <v>389</v>
+      </c>
+      <c r="C188" t="s">
+        <v>13</v>
+      </c>
+      <c r="E188" t="s">
+        <v>391</v>
+      </c>
+      <c r="H188">
+        <v>832</v>
+      </c>
+      <c r="I188">
+        <v>965</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>